--- a/parameters/UA/ammonia/transport_parameters.xlsx
+++ b/parameters/UA/ammonia/transport_parameters.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10119"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/samiyhanaqvi/Desktop/SHIELD/restructuring_and_integration/GeoX/parameters/NA/ammonia/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\engs2859\Desktop\Geo-X\Geo-X\parameters\UA\ammonia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEEF7906-58F5-6541-9335-FA677A6655AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{241304C5-8A76-4F7D-9F64-393FF9B185FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17240" xr2:uid="{01CAD706-003C-4A74-9F03-CC297AE4FC2E}"/>
+    <workbookView xWindow="3630" yWindow="4350" windowWidth="16770" windowHeight="9330" xr2:uid="{01CAD706-003C-4A74-9F03-CC297AE4FC2E}"/>
   </bookViews>
   <sheets>
     <sheet name="NH3" sheetId="4" r:id="rId1"/>
@@ -437,49 +437,49 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2336249F-38D8-48A5-AB33-F1F0C167058D}">
   <dimension ref="A1:B16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4">
-        <v>1.01</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -487,7 +487,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -495,15 +495,15 @@
         <v>160000</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
       <c r="B8">
-        <v>193597</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+        <v>160000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -511,7 +511,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -519,7 +519,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -527,15 +527,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
       <c r="B12">
-        <v>225994</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+        <v>210000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -543,15 +543,15 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>15</v>
       </c>
       <c r="B14" s="1">
-        <v>14700</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -559,7 +559,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>14</v>
       </c>
